--- a/outputs/reports/gradient_boosting_v2/feature_importance_top10.xlsx
+++ b/outputs/reports/gradient_boosting_v2/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1671891555341897</v>
+        <v>0.2374525038280519</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02745224643529737</v>
+        <v>0.05506779170600101</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=16.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1437700029492355</v>
+        <v>0.1477847722389224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02360685140346158</v>
+        <v>0.03427287951810748</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=14.38%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=14.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1015303280210568</v>
+        <v>0.1318739484678361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01667115056945573</v>
+        <v>0.03058298821280653</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=13.19%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09202722039563266</v>
+        <v>0.08831294857495794</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01511075239888809</v>
+        <v>0.02048072342328378</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=8.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0667729849588727</v>
+        <v>0.04938341619564358</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01096403909963239</v>
+        <v>0.01145254580579913</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.68%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06537482659559163</v>
+        <v>0.04835000031506613</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01073446327683619</v>
+        <v>0.01121288553884098</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>NTS_BT_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>국세청업종코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05499786999311703</v>
+        <v>0.03432327013113043</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009030580217020967</v>
+        <v>0.007959935817811348</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 국세청업종코드(NTS_BT_CD). 기여도(정규화 비중)=3.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04788692394236856</v>
+        <v>0.03111590011153352</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007862971930768625</v>
+        <v>0.007216112184386392</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.79%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.11%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.04465368272728172</v>
+        <v>0.02727839845743778</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007332077840552509</v>
+        <v>0.00632615424184052</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=4.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=2.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.04365967951588676</v>
+        <v>0.02534389433952774</v>
       </c>
       <c r="F11" t="n">
-        <v>0.007168863779033363</v>
+        <v>0.005877521912839634</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=4.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=2.53%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
